--- a/AtchisonRegime/Outputs/UK/MSCI_UK 100/df_regTrendSummaryMSCI_UK 100.xlsx
+++ b/AtchisonRegime/Outputs/UK/MSCI_UK 100/df_regTrendSummaryMSCI_UK 100.xlsx
@@ -1396,13 +1396,13 @@
         <v>45747</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.02039999999999997</v>
+        <v>-0.04038383999999995</v>
       </c>
     </row>
   </sheetData>
